--- a/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="物品道具" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="掉落归属导航" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="非背包与待设计" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="功能调用链" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品道具" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落归属导航" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非背包与待设计" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能调用链" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -553,9 +553,6 @@
           <t>物品道具账本</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
@@ -576,9 +573,6 @@
           <t>可掉落到地面、拾取进入背包的物品；内容ID唯一。子弹、通用弹药、配件及成品武器归武器账本。</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -1886,12 +1880,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
+          <t>ITM-CONSUMABLE-ITEM-HEALTH-POTION</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A33</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1901,7 +1895,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/props/health_potion/source/itm_health_potion_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1967,12 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-S</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A32</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -1988,7 +1982,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；无对应资产主表登记，不新增AssetID；电池使用动作存在，模型仍落入crate兜底</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；无对应资产主表登记，不新增AssetID；电池使用动作存在，模型仍落入crate兜底；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/props/battery_small/source/itm_battery_small_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2050,12 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-L</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2071,7 +2065,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；无对应资产主表登记，不新增AssetID；电池使用动作存在，模型仍落入crate兜底</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；无对应资产主表登记，不新增AssetID；电池使用动作存在，模型仍落入crate兜底；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/props/battery_large/source/itm_battery_large_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
         </is>
       </c>
     </row>
@@ -2584,9 +2578,6 @@
           <t>怪物掉落归属导航</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
@@ -2600,9 +2591,6 @@
           <t>每行对应原CSV一行，仅指向登记所有者与运行投影。概率、数量与权重仍以原作者表及运行配置为准。</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -3588,8 +3576,6 @@
           <t>非背包产出与待设计</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -3597,8 +3583,6 @@
           <t>货币与未注册设计条目显式排除，不冒充当前可入包物品。</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -3693,9 +3677,6 @@
           <t>物品功能调用链</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -3703,9 +3684,6 @@
           <t>账本仅导航；运行时不读取此XLSX，不另设物品、掉落或背包状态所有者。</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>

--- a/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
@@ -167,8 +167,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryItems" displayName="InventoryItems" ref="A4:Q24" headerRowCount="1">
-  <autoFilter ref="A4:Q24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryItems" displayName="InventoryItems" ref="A4:Q25" headerRowCount="1">
+  <autoFilter ref="A4:Q25"/>
   <tableColumns count="17">
     <tableColumn id="1" name="内容ID"/>
     <tableColumn id="2" name="名称"/>
@@ -193,8 +193,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DropNavigation" displayName="DropNavigation" ref="A4:J20" headerRowCount="1">
-  <autoFilter ref="A4:J20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DropNavigation" displayName="DropNavigation" ref="A4:J17" headerRowCount="1">
+  <autoFilter ref="A4:J17"/>
   <tableColumns count="10">
     <tableColumn id="1" name="作者表行"/>
     <tableColumn id="2" name="关卡ID"/>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L482</t>
+          <t>src/base/ItemRegistry.gd#L514</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L482 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L514 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L511</t>
+          <t>src/base/ItemRegistry.gd#L543</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L511 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L543 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L540</t>
+          <t>src/base/ItemRegistry.gd#L572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L540 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L572 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1384,308 +1384,308 @@
     <row r="13" ht="93" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>bp_starter_rifle</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>初始步枪蓝图碎片</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>blueprint</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L601</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>缺行</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L601 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>src/game/ItemUseHandler.gd#apply / unlock_blueprint</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>blueprint；程序几何</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>未登记</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>未登记</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；内容数据库缺行，运行注册表有此ID；无对应资产主表登记，不新增AssetID</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="93" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>bp_rifle</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>步枪蓝图碎片</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>blueprint</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>gun_body</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L576</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L637</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A15</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L576 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, loot_common, spawn_starter, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2, combat_floor_3</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L637 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, loot_common, spawn_starter, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2, combat_floor_3</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>src/game/ItemUseHandler.gd#apply / unlock_blueprint</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>blueprint；程序几何</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>未登记</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>未登记</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="76" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>bp_machinegun</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>蜂窝机枪蓝图碎片</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>blueprint</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>gun_body</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L606</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L667</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A13</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L606 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L667 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>src/game/ItemUseHandler.gd#apply / unlock_blueprint</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>blueprint；程序几何</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>未登记</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>未登记</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="93" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16" ht="93" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>bp_sniper</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>弹弓狙击蓝图碎片</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>blueprint</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>gun_body</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L633</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L694</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A17</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L633 / loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, loot_common, spawn_starter</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>src/game/InventoryModule.gd#add_item</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>src/game/ItemUseHandler.gd#apply / unlock_blueprint</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>blueprint；程序几何</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="76" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>bp_launcher</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>反胃榴弹筒蓝图碎片</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>blueprint</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>gun_body</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L662</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A12</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>未在当前CSV列出；池来源见下一列</t>
-        </is>
-      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L662 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
+          <t>src/base/ItemRegistry.gd#L694 / loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, loot_common, spawn_starter</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1732,12 +1732,12 @@
     <row r="17" ht="76" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>bp_charge</t>
+          <t>bp_launcher</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>蓄力萝卜炮蓝图碎片</t>
+          <t>反胃榴弹筒蓝图碎片</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L687</t>
+          <t>src/base/ItemRegistry.gd#L723</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A11</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L687 / loot_abyss, boss_floor_2, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L723 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1819,20 +1819,24 @@
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>item_health_potion</t>
+          <t>bp_charge</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>治疗药水</t>
+          <t>蓄力萝卜炮蓝图碎片</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>consumable</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>blueprint</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>gun_body</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
@@ -1840,12 +1844,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L718</t>
+          <t>src/base/ItemRegistry.gd#L748</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A20</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A11</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1855,7 +1859,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L718 / loot_common, loot_floor_1_2, loot_floor_3_4, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L748 / loot_abyss, boss_floor_2, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1865,7 +1869,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>src/game/ItemUseHandler.gd#apply / heal</t>
+          <t>src/game/ItemUseHandler.gd#apply / unlock_blueprint</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1875,17 +1879,17 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>heal；程序罐体</t>
+          <t>blueprint；程序几何</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>ITM-CONSUMABLE-ITEM-HEALTH-POTION</t>
+          <t>未登记</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A33</t>
+          <t>未登记</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1895,19 +1899,19 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/props/health_potion/source/itm_health_potion_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>item_battery_s</t>
+          <t>item_health_potion</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小型电池</t>
+          <t>治疗药水</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1915,11 +1919,7 @@
           <t>consumable</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
+      <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L760</t>
+          <t>src/base/ItemRegistry.gd#L779</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A41</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A20</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行13 / exploder</t>
+          <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L760 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L779 / loot_common, loot_floor_1_2, loot_floor_3_4, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>src/game/ItemUseHandler.gd#apply / restore_flashlight_charge</t>
+          <t>src/game/ItemUseHandler.gd#apply / heal</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>crate；通用箱体，尚无专用外观</t>
+          <t>heal；程序罐体</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>ITM-CONSUMABLE-ITEM-BATTERY-S</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A32</t>
+          <t>ITM-CONSUMABLE-ITEM-HEALTH-POTION</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A33</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -1982,19 +1982,19 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；无对应资产主表登记，不新增AssetID；电池使用动作存在，模型仍落入crate兜底；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/props/battery_small/source/itm_battery_small_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="76" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>item_battery_l</t>
+          <t>item_battery_s</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>大型电池</t>
+          <t>小型电池</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2002,7 +2002,11 @@
           <t>consumable</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
@@ -2010,22 +2014,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L784</t>
+          <t>src/base/ItemRegistry.gd#L821</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A42</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A41</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行14 / exploder</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行11 / exploder</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L784 / loot_floor_3_4, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, elite_floor_1, elite_floor_2, boss_floor_1</t>
+          <t>src/base/ItemRegistry.gd#L821 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -2050,12 +2054,12 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>ITM-CONSUMABLE-ITEM-BATTERY-L</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A31</t>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-S</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A32</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2065,19 +2069,19 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；无对应资产主表登记，不新增AssetID；电池使用动作存在，模型仍落入crate兜底；2026-10-14 Blender源已完成（未导入运行时）：art_source/items_weapons/props/battery_large/source/itm_battery_large_source_v001.blend；preview/ground双模型源已完成，ground100–200三角，运行时用途分流待接入。</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；电池使用动作存在，模型仍落入crate兜底</t>
         </is>
       </c>
     </row>
     <row r="21" ht="76" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>item_cell_pack</t>
+          <t>item_battery_l</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>电芯包</t>
+          <t>大型电池</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2093,22 +2097,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L806</t>
+          <t>src/base/ItemRegistry.gd#L845</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A43</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>未在当前CSV列出；池来源见下一列</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行12 / exploder</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L806 / loot_floor_5, loot_abyss, boss_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L845 / loot_floor_3_4, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, elite_floor_1, elite_floor_2, boss_floor_1</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2133,12 +2137,12 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-L</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2148,31 +2152,27 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；电池使用动作存在，模型仍落入crate兜底</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；电池使用动作存在，模型仍落入crate兜底</t>
         </is>
       </c>
     </row>
     <row r="22" ht="76" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>item_flashlight_basic</t>
+          <t>item_cell_pack</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>基础模块</t>
+          <t>电芯包</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>module</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>flashlight_module</t>
-        </is>
-      </c>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L832</t>
+          <t>src/base/ItemRegistry.gd#L867</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A44</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A43</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L832 / 无池声明</t>
+          <t>src/base/ItemRegistry.gd#L867 / loot_floor_5, loot_abyss, boss_floor_2</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>src/game/ItemUseHandler.gd#apply / equip_flashlight_module</t>
+          <t>src/game/ItemUseHandler.gd#apply / restore_flashlight_charge</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -2235,19 +2235,19 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；使用需设施上下文，入包不等于可在战局切换</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；电池使用动作存在，模型仍落入crate兜底</t>
         </is>
       </c>
     </row>
     <row r="23" ht="76" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>item_flashlight_advanced</t>
+          <t>item_flashlight_basic</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>加强模块</t>
+          <t>基础模块</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L845</t>
+          <t>src/base/ItemRegistry.gd#L893</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A45</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A44</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L845 / blueprint_attachment_unlock</t>
+          <t>src/base/ItemRegistry.gd#L893 / 无池声明</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2329,85 +2329,172 @@
     <row r="24" ht="76" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>item_flashlight_advanced</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>加强模块</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>flashlight_module</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L906</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A45</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L906 / blueprint_attachment_unlock</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>src/game/ItemUseHandler.gd#apply / equip_flashlight_module</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>crate；通用箱体，尚无专用外观</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>未登记</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>未登记</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；使用需设施上下文，入包不等于可在战局切换</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>item_flashlight_efficient</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>节能模块</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>flashlight_module</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L862</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L923</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A46</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L862 / elite_floor_1, elite_floor_2, boss_floor_2</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L923 / elite_floor_1, elite_floor_2, boss_floor_2</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>src/game/ItemUseHandler.gd#apply / equip_flashlight_module</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>crate；通用箱体，尚无专用外观</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>未登记</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>未登记</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；使用需设施上下文，入包不等于可在战局切换</t>
         </is>
@@ -2472,81 +2559,89 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId132"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId125"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId133"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2557,7 +2652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2747,7 +2842,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A13</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A14</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2799,7 +2894,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A17</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2851,7 +2946,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A16</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A17</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2883,27 +2978,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>melee_chaser</t>
+          <t>ranged_caster</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>@currency:extraction_points</t>
+          <t>mod_bullet_piercing</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>魂</t>
+          <t>穿甲弹模块</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>货币；不进入背包</t>
+          <t>武器账本</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_grant_run_currency</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2940,12 +3035,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>mod_bullet_piercing</t>
+          <t>mod_bullet_bounce</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>穿甲弹模块</t>
+          <t>回旋镖弹模块</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2992,12 +3087,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>mod_bullet_bounce</t>
+          <t>attach_scope</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>回旋镖弹模块</t>
+          <t>放大镜瞄具</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3007,7 +3102,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A19</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -3044,12 +3139,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>attach_scope</t>
+          <t>item_ammo_pack</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>放大镜瞄具</t>
+          <t>通用弹药</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3059,7 +3154,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A27</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A17</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -3091,17 +3186,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ranged_caster</t>
+          <t>exploder</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>item_ammo_pack</t>
+          <t>mod_bullet_explosive</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>通用弹药</t>
+          <t>爆炸弹模块</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3111,7 +3206,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A16</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -3143,27 +3238,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ranged_caster</t>
+          <t>exploder</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>@currency:extraction_points</t>
+          <t>item_battery_s</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>魂</t>
+          <t>小型电池</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>货币；不进入背包</t>
+          <t>物品道具账本</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>src/world3d/Dungeon3D.gd#_grant_run_currency</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -3200,22 +3295,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>mod_bullet_explosive</t>
+          <t>item_battery_l</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>爆炸弹模块</t>
+          <t>大型电池</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>武器账本</t>
+          <t>物品道具账本</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A21</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3252,22 +3347,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>item_battery_s</t>
+          <t>weapon_launcher</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>小型电池</t>
+          <t>反胃榴弹筒</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>物品道具账本</t>
+          <t>武器账本</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A19</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A12</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -3304,22 +3399,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>item_battery_l</t>
+          <t>item_ammo_pack</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>大型电池</t>
+          <t>通用弹药</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>物品道具账本</t>
+          <t>武器账本</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -3333,162 +3428,6 @@
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>src/rewards/RuntimeRewardCoordinator.gd#configure_level_drop_table / resolve_kill</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行15</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>expedition_01</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>exploder</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>weapon_launcher</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>反胃榴弹筒</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>武器账本</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A11</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>data/level_plans/expedition_01/level_plan.json#monster_drop_table.rows[13]</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>src/rewards/MonsterDropTable.gd#compile</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>src/rewards/RuntimeRewardCoordinator.gd#configure_level_drop_table / resolve_kill</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行16</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>expedition_01</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>exploder</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>item_ammo_pack</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>通用弹药</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>武器账本</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A16</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>data/level_plans/expedition_01/level_plan.json#monster_drop_table.rows[14]</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>src/rewards/MonsterDropTable.gd#compile</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>src/rewards/RuntimeRewardCoordinator.gd#configure_level_drop_table / resolve_kill</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行17</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>expedition_01</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>exploder</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>@currency:extraction_points</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>魂</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>货币；不进入背包</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>src/world3d/Dungeon3D.gd#_grant_run_currency</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>data/level_plans/expedition_01/level_plan.json#monster_drop_table.rows[15]</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>src/rewards/MonsterDropTable.gd#compile</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>src/rewards/RuntimeRewardCoordinator.gd#configure_level_drop_table / resolve_kill</t>
         </is>
@@ -3539,19 +3478,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId49"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId40"/>
   </tableParts>
 </worksheet>
 </file>

--- a/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
@@ -167,8 +167,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryItems" displayName="InventoryItems" ref="A4:Q25" headerRowCount="1">
-  <autoFilter ref="A4:Q25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InventoryItems" displayName="InventoryItems" ref="A4:Q26" headerRowCount="1">
+  <autoFilter ref="A4:Q26"/>
   <tableColumns count="17">
     <tableColumn id="1" name="内容ID"/>
     <tableColumn id="2" name="名称"/>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -553,6 +553,9 @@
           <t>物品道具账本</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
@@ -570,9 +573,12 @@
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>可掉落到地面、拾取进入背包的物品；内容ID唯一。子弹、通用弹药、配件及成品武器归武器账本。</t>
-        </is>
-      </c>
+          <t>可掉落到地面、拾取进入背包的物品；内容ID唯一。子弹模块、配件及成品武器归武器账本；通用弹药归道具。</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -752,7 +758,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>beacon；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/beacon/runtime/itm_beacon_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -835,7 +841,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>key；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/room_key/runtime/itm_room_key_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1183,17 +1189,17 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>blueprint；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A39</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1203,7 +1209,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
@@ -1270,17 +1276,17 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>blueprint；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A39</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1290,7 +1296,7 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1363,17 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>blueprint；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A39</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1377,7 +1383,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；内容数据库缺行，运行注册表有此ID；无对应资产主表登记，不新增AssetID</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；内容数据库缺行，运行注册表有此ID</t>
         </is>
       </c>
     </row>
@@ -1444,17 +1450,17 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>blueprint；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A39</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1464,7 +1470,7 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；内容数据库缺行，运行注册表有此ID；无对应资产主表登记，不新增AssetID</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；内容数据库缺行，运行注册表有此ID</t>
         </is>
       </c>
     </row>
@@ -1531,17 +1537,17 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>blueprint；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A39</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1551,7 +1557,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
@@ -1618,17 +1624,17 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>blueprint；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A39</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1638,7 +1644,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
@@ -1705,17 +1711,17 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>blueprint；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A39</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1725,11 +1731,11 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="76" customHeight="1">
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="59" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>bp_launcher</t>
@@ -1792,17 +1798,17 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>blueprint；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A39</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1812,11 +1818,11 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="76" customHeight="1">
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="59" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>bp_charge</t>
@@ -1879,17 +1885,17 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>blueprint；程序几何</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A39</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1899,7 +1905,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1968,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>heal；程序罐体</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/health_potion/runtime/itm_health_potion_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1986,15 +1992,15 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="76" customHeight="1">
+    <row r="20" ht="110" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>item_battery_s</t>
+          <t>item_ammo_pack</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>小型电池</t>
+          <t>通用弹药</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2002,11 +2008,7 @@
           <t>consumable</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
@@ -2014,22 +2016,24 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L821</t>
+          <t>src/base/ItemRegistry.gd#L800</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A41</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A18</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行11 / exploder</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行5 / melee_chaser
+docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行9 / ranged_caster
+docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行14 / exploder</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L821 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L800 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -2039,7 +2043,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>src/game/ItemUseHandler.gd#apply / restore_flashlight_charge</t>
+          <t>src/world3d/Dungeon3D.gd#_on_inventory_item_clicked</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -2049,17 +2053,17 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>crate；通用箱体，尚无专用外观</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_standard/runtime/wpn_bullet_standard_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>ITM-CONSUMABLE-ITEM-BATTERY-S</t>
+          <t>ITM-CONSUMABLE-ITEM-AMMO-PACK</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A32</t>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A34</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2069,19 +2073,19 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；电池使用动作存在，模型仍落入crate兜底</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
         </is>
       </c>
     </row>
     <row r="21" ht="76" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>item_battery_l</t>
+          <t>item_battery_s</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>大型电池</t>
+          <t>小型电池</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2089,7 +2093,11 @@
           <t>consumable</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
@@ -2097,22 +2105,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L845</t>
+          <t>src/base/ItemRegistry.gd#L821</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A42</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行12 / exploder</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行11 / exploder</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L845 / loot_floor_3_4, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, elite_floor_1, elite_floor_2, boss_floor_1</t>
+          <t>src/base/ItemRegistry.gd#L821 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2132,17 +2140,17 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>crate；通用箱体，尚无专用外观</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/battery_small/runtime/itm_battery_small_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>ITM-CONSUMABLE-ITEM-BATTERY-L</t>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-S</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A31</t>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2152,19 +2160,19 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；电池使用动作存在，模型仍落入crate兜底</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
         </is>
       </c>
     </row>
     <row r="22" ht="76" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>item_cell_pack</t>
+          <t>item_battery_l</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>电芯包</t>
+          <t>大型电池</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2180,161 +2188,157 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
+          <t>src/base/ItemRegistry.gd#L845</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A42</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行12 / exploder</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L845 / loot_floor_3_4, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, elite_floor_1, elite_floor_2, boss_floor_1</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>src/game/ItemUseHandler.gd#apply / restore_flashlight_charge</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/battery_large/runtime/itm_battery_large_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-L</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A31</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="59" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>item_cell_pack</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>电芯包</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
           <t>src/base/ItemRegistry.gd#L867</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A43</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>src/base/ItemRegistry.gd#L867 / loot_floor_5, loot_abyss, boss_floor_2</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>src/game/ItemUseHandler.gd#apply / restore_flashlight_charge</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>crate；通用箱体，尚无专用外观</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/cell_pack/runtime/itm_cell_pack_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-CELL-PACK</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A35</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；电池使用动作存在，模型仍落入crate兜底</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="76" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>item_flashlight_basic</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>基础模块</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>module</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>flashlight_module</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L893</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A44</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>未在当前CSV列出；池来源见下一列</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>src/base/ItemRegistry.gd#L893 / 无池声明</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>src/game/InventoryModule.gd#add_item</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>src/game/ItemUseHandler.gd#apply / equip_flashlight_module</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>crate；通用箱体，尚无专用外观</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；使用需设施上下文，入包不等于可在战局切换</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="76" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>item_flashlight_advanced</t>
+          <t>item_flashlight_basic</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>加强模块</t>
+          <t>基础模块</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2354,12 +2358,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L906</t>
+          <t>src/base/ItemRegistry.gd#L893</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A45</t>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A44</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2369,7 +2373,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L906 / blueprint_attachment_unlock</t>
+          <t>src/base/ItemRegistry.gd#L893 / 无池声明</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2389,17 +2393,17 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>crate；通用箱体，尚无专用外观</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/flashlight_basic/runtime/itm_flashlight_basic_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
+          <t>ITM-MODULE-FLASHLIGHT-BASIC</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A36</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2409,94 +2413,181 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；使用需设施上下文，入包不等于可在战局切换</t>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；使用需设施上下文，入包不等于可在战局切换</t>
         </is>
       </c>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>item_flashlight_advanced</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>加强模块</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>flashlight_module</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L906</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A45</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>未在当前CSV列出；池来源见下一列</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>src/base/ItemRegistry.gd#L906 / blueprint_attachment_unlock</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>src/game/InventoryModule.gd#add_item</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>src/game/ItemUseHandler.gd#apply / equip_flashlight_module</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/flashlight_advanced/runtime/itm_flashlight_advanced_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-ADVANCED</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A37</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；使用需设施上下文，入包不等于可在战局切换</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>item_flashlight_efficient</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>节能模块</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>flashlight_module</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>src/base/ItemRegistry.gd#L923</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>docs/v0.1/data/ShellStorm2_游戏内容数据库_v010.xlsx#掉落物品!A46</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>未在当前CSV列出；池来源见下一列</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>src/base/ItemRegistry.gd#L923 / elite_floor_1, elite_floor_2, boss_floor_2</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>src/game/InventoryModule.gd#add_item</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>src/game/ItemUseHandler.gd#apply / equip_flashlight_module</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>src/world3d/ItemModelFactory3D.gd#create_model / get_model_kind</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>crate；通用箱体，尚无专用外观</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>未登记</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/flashlight_efficient/runtime/itm_flashlight_efficient_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-EFFICIENT</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx#资产主表!A38</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>WORLD-LOOT / REWARD-SERVICE / INVENTORY-SLOTS</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；无对应资产主表登记，不新增AssetID；使用需设施上下文，入包不等于可在战局切换</t>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>已注册；本表只导航，堆叠/数值/掉落概率由原定义拥有；远征01作者掉落表未列此项（不可视为无其他产出）；使用需设施上下文，入包不等于可在战局切换</t>
         </is>
       </c>
     </row>
@@ -2547,101 +2638,121 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId152"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId133"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId153"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2673,6 +2784,9 @@
           <t>怪物掉落归属导航</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
@@ -2686,6 +2800,9 @@
           <t>每行对应原CSV一行，仅指向登记所有者与运行投影。概率、数量与权重仍以原作者表及运行配置为准。</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -2894,7 +3011,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A18</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2941,12 +3058,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>武器账本</t>
+          <t>物品道具账本</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A17</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2998,7 +3115,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A21</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A20</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -3050,7 +3167,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A20</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A19</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -3102,7 +3219,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A28</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -3149,12 +3266,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>武器账本</t>
+          <t>物品道具账本</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A17</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -3206,7 +3323,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A22</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -3258,7 +3375,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A21</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -3310,7 +3427,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A21</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3409,12 +3526,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>武器账本</t>
+          <t>物品道具账本</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A17</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -3506,6 +3623,8 @@
           <t>非背包产出与待设计</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -3513,6 +3632,8 @@
           <t>货币与未注册设计条目显式排除，不冒充当前可入包物品。</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -3607,6 +3728,9 @@
           <t>物品功能调用链</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -3614,6 +3738,9 @@
           <t>账本仅导航；运行时不读取此XLSX，不另设物品、掉落或背包状态所有者。</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>

--- a/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L67</t>
+          <t>src/base/ItemRegistry.gd#L152</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L67 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, elite_floor_1, elite_floor_2, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L152 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_1, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, elite_floor_1, elite_floor_2, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/beacon/runtime/itm_beacon_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/beacon/runtime/itm_beacon_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="76" customHeight="1">
+    <row r="6" ht="110" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>item_room_key</t>
@@ -806,7 +806,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L98</t>
+          <t>src/base/ItemRegistry.gd#L183</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L98 / loot_common, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, elite_floor_1, elite_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L183 / loot_common, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, elite_floor_1, elite_floor_2</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/room_key/runtime/itm_room_key_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/room_key/runtime/itm_room_key_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="59" customHeight="1">
+    <row r="7" ht="110" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>equipment_backpack_2</t>
@@ -893,7 +893,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L121</t>
+          <t>src/base/ItemRegistry.gd#L206</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L121 / loot_common, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L206 / loot_common, loot_floor_1_2, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>backpack；专用PackedScene，账本仍待制作</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/backpack_small/runtime/prp_backpack_small_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -952,7 +952,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="76" customHeight="1">
+    <row r="8" ht="110" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>equipment_backpack_4</t>
@@ -980,7 +980,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L142</t>
+          <t>src/base/ItemRegistry.gd#L227</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L142 / loot_floor_1_2, loot_floor_3_4, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, elite_floor_1, elite_floor_2, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L227 / loot_floor_1_2, loot_floor_3_4, scavenge_floor_2, scavenge_floor_3, scavenge_floor_4, elite_floor_1, elite_floor_2, combat_floor_3</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>backpack；专用PackedScene，账本仍待制作</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/backpack_medium/runtime/prp_backpack_medium_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="76" customHeight="1">
+    <row r="9" ht="110" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>equipment_backpack_8</t>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L165</t>
+          <t>src/base/ItemRegistry.gd#L250</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L165 / loot_floor_5, loot_abyss, scavenge_floor_4, scavenge_floor_5, elite_floor_2, boss_floor_1, boss_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L250 / loot_floor_5, loot_abyss, scavenge_floor_4, scavenge_floor_5, elite_floor_2, boss_floor_1, boss_floor_2</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>backpack；专用PackedScene，账本仍待制作</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/backpack_large/runtime/prp_backpack_large_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="93" customHeight="1">
+    <row r="10" ht="110" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>bp_pistol</t>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L514</t>
+          <t>src/base/ItemRegistry.gd#L599</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L514 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L599 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="93" customHeight="1">
+    <row r="11" ht="110" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>bp_shotgun</t>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L543</t>
+          <t>src/base/ItemRegistry.gd#L628</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L543 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L628 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="93" customHeight="1">
+    <row r="12" ht="110" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>bp_sprinkler</t>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L572</t>
+          <t>src/base/ItemRegistry.gd#L657</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L572 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L657 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="93" customHeight="1">
+    <row r="13" ht="110" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>bp_starter_rifle</t>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L601</t>
+          <t>src/base/ItemRegistry.gd#L686</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L601 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L686 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="93" customHeight="1">
+    <row r="14" ht="110" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>bp_rifle</t>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L637</t>
+          <t>src/base/ItemRegistry.gd#L722</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L637 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, loot_common, spawn_starter, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L722 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, loot_common, spawn_starter, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2, combat_floor_3</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="76" customHeight="1">
+    <row r="15" ht="110" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>bp_machinegun</t>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L667</t>
+          <t>src/base/ItemRegistry.gd#L752</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L667 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L752 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="93" customHeight="1">
+    <row r="16" ht="110" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>bp_sniper</t>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L694</t>
+          <t>src/base/ItemRegistry.gd#L779</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L694 / loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, loot_common, spawn_starter</t>
+          <t>src/base/ItemRegistry.gd#L779 / loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, loot_common, spawn_starter</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="59" customHeight="1">
+    <row r="17" ht="110" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>bp_launcher</t>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L723</t>
+          <t>src/base/ItemRegistry.gd#L808</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L723 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
+          <t>src/base/ItemRegistry.gd#L808 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="59" customHeight="1">
+    <row r="18" ht="110" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>bp_charge</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L748</t>
+          <t>src/base/ItemRegistry.gd#L833</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L748 / loot_abyss, boss_floor_2, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L833 / loot_abyss, boss_floor_2, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="76" customHeight="1">
+    <row r="19" ht="110" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>item_health_potion</t>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L779</t>
+          <t>src/base/ItemRegistry.gd#L864</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L779 / loot_common, loot_floor_1_2, loot_floor_3_4, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L864 / loot_common, loot_floor_1_2, loot_floor_3_4, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/health_potion/runtime/itm_health_potion_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/health_potion/runtime/itm_health_potion_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L800</t>
+          <t>src/base/ItemRegistry.gd#L885</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L800 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L885 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_standard/runtime/wpn_bullet_standard_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/weapons/bullet_standard/runtime/wpn_bullet_standard_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="76" customHeight="1">
+    <row r="21" ht="110" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>item_battery_s</t>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L821</t>
+          <t>src/base/ItemRegistry.gd#L906</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L821 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L906 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/battery_small/runtime/itm_battery_small_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/battery_small/runtime/itm_battery_small_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="76" customHeight="1">
+    <row r="22" ht="110" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>item_battery_l</t>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L845</t>
+          <t>src/base/ItemRegistry.gd#L930</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L845 / loot_floor_3_4, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, elite_floor_1, elite_floor_2, boss_floor_1</t>
+          <t>src/base/ItemRegistry.gd#L930 / loot_floor_3_4, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, elite_floor_1, elite_floor_2, boss_floor_1</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/battery_large/runtime/itm_battery_large_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/battery_large/runtime/itm_battery_large_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="59" customHeight="1">
+    <row r="23" ht="110" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>item_cell_pack</t>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L867</t>
+          <t>src/base/ItemRegistry.gd#L952</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L867 / loot_floor_5, loot_abyss, boss_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L952 / loot_floor_5, loot_abyss, boss_floor_2</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/cell_pack/runtime/itm_cell_pack_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/cell_pack/runtime/itm_cell_pack_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="76" customHeight="1">
+    <row r="24" ht="110" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>item_flashlight_basic</t>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L893</t>
+          <t>src/base/ItemRegistry.gd#L978</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L893 / 无池声明</t>
+          <t>src/base/ItemRegistry.gd#L978 / 无池声明</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/flashlight_basic/runtime/itm_flashlight_basic_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/flashlight_basic/runtime/itm_flashlight_basic_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="76" customHeight="1">
+    <row r="25" ht="127" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>item_flashlight_advanced</t>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L906</t>
+          <t>src/base/ItemRegistry.gd#L991</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L906 / blueprint_attachment_unlock</t>
+          <t>src/base/ItemRegistry.gd#L991 / blueprint_attachment_unlock</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/flashlight_advanced/runtime/itm_flashlight_advanced_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/flashlight_advanced/runtime/itm_flashlight_advanced_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="76" customHeight="1">
+    <row r="26" ht="127" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>item_flashlight_efficient</t>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L923</t>
+          <t>src/base/ItemRegistry.gd#L1008</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L923 / elite_floor_1, elite_floor_2, boss_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1008 / elite_floor_1, elite_floor_2, boss_floor_2</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/flashlight_efficient/runtime/itm_flashlight_efficient_ground_root_top3d.tscn</t>
+          <t>已接入3D资产；地面/图标共用：assets/art/items_weapons/props/flashlight_efficient/runtime/itm_flashlight_efficient_ground_root_top3d.tscn；物品专用色板：assets/art/shared/palette/item_high_visibility_palette_10x10_512.png（HSV S/V×1.61；物品独立四材质；图标本色补光0.45）</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>魂直接入货币余额，不占背包格</t>
+          <t>金币直接入货币余额，不占背包格</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
+    <row r="13" ht="59" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>拾取事务</t>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>魂走货币；物品走add_item，满包保留、部分接收保留余量</t>
+          <t>金币走货币；物品走add_item，满包保留、部分接收保留余量</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品道具" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落归属导航" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非背包与待设计" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能调用链" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="物品道具" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="掉落归属导航" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="非背包与待设计" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="功能调用链" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -193,8 +193,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DropNavigation" displayName="DropNavigation" ref="A4:J17" headerRowCount="1">
-  <autoFilter ref="A4:J17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DropNavigation" displayName="DropNavigation" ref="A4:J15" headerRowCount="1">
+  <autoFilter ref="A4:J15"/>
   <tableColumns count="10">
     <tableColumn id="1" name="作者表行"/>
     <tableColumn id="2" name="关卡ID"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L599</t>
+          <t>src/base/ItemRegistry.gd#L594</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L599 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L594 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L628</t>
+          <t>src/base/ItemRegistry.gd#L623</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L628 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L623 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L657</t>
+          <t>src/base/ItemRegistry.gd#L652</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L657 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L652 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L686</t>
+          <t>src/base/ItemRegistry.gd#L681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L686 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L681 / loot_floor_1_2, loot_floor_3_4, loot_floor_5, loot_abyss, loot_common, spawn_starter, scavenge_floor_1, scavenge_floor_2, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L722</t>
+          <t>src/base/ItemRegistry.gd#L717</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L722 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, loot_common, spawn_starter, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L717 / loot_floor_3_4, loot_floor_5, loot_abyss, boss_floor_1, loot_common, spawn_starter, scavenge_floor_3, scavenge_floor_4, combat_floor_1, combat_floor_2, combat_floor_3</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L752</t>
+          <t>src/base/ItemRegistry.gd#L747</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L752 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L747 / loot_floor_3_4, loot_floor_5, loot_abyss, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, combat_floor_1, combat_floor_2</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L779</t>
+          <t>src/base/ItemRegistry.gd#L774</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L779 / loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, loot_common, spawn_starter</t>
+          <t>src/base/ItemRegistry.gd#L774 / loot_floor_5, loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4, combat_floor_5, loot_common, spawn_starter</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L808</t>
+          <t>src/base/ItemRegistry.gd#L803</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L808 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
+          <t>src/base/ItemRegistry.gd#L803 / loot_abyss, boss_floor_1, boss_floor_2, scavenge_floor_5, combat_floor_3, combat_floor_4</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L833</t>
+          <t>src/base/ItemRegistry.gd#L828</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L833 / loot_abyss, boss_floor_2, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L828 / loot_abyss, boss_floor_2, scavenge_floor_5, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L864</t>
+          <t>src/base/ItemRegistry.gd#L859</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L864 / loot_common, loot_floor_1_2, loot_floor_3_4, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3</t>
+          <t>src/base/ItemRegistry.gd#L859 / loot_common, loot_floor_1_2, loot_floor_3_4, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L885</t>
+          <t>src/base/ItemRegistry.gd#L880</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -2026,14 +2026,14 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行5 / melee_chaser
-docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行9 / ranged_caster
-docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行14 / exploder</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行4 / melee_chaser
+docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行8 / ranged_caster
+docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行12 / exploder</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L885 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L880 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L906</t>
+          <t>src/base/ItemRegistry.gd#L901</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行11 / exploder</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行10 / exploder</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L906 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
+          <t>src/base/ItemRegistry.gd#L901 / loot_common, loot_floor_1_2, spawn_starter, combat_floor_1, combat_floor_2, combat_floor_3, combat_floor_4, combat_floor_5</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L930</t>
+          <t>src/base/ItemRegistry.gd#L925</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行12 / exploder</t>
+          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行11 / exploder</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L930 / loot_floor_3_4, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, elite_floor_1, elite_floor_2, boss_floor_1</t>
+          <t>src/base/ItemRegistry.gd#L925 / loot_floor_3_4, scavenge_floor_3, scavenge_floor_4, scavenge_floor_5, elite_floor_1, elite_floor_2, boss_floor_1</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L952</t>
+          <t>src/base/ItemRegistry.gd#L947</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L952 / loot_floor_5, loot_abyss, boss_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L947 / loot_floor_5, loot_abyss, boss_floor_2</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L978</t>
+          <t>src/base/ItemRegistry.gd#L973</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L978 / 无池声明</t>
+          <t>src/base/ItemRegistry.gd#L973 / 无池声明</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L991</t>
+          <t>src/base/ItemRegistry.gd#L986</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L991 / blueprint_attachment_unlock</t>
+          <t>src/base/ItemRegistry.gd#L986 / blueprint_attachment_unlock</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1008</t>
+          <t>src/base/ItemRegistry.gd#L1003</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd#L1008 / elite_floor_1, elite_floor_2, boss_floor_2</t>
+          <t>src/base/ItemRegistry.gd#L1003 / elite_floor_1, elite_floor_2, boss_floor_2</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>weapon_pistol</t>
+          <t>weapon_baseball_bat</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>豌豆手枪</t>
+          <t>废土棒球棍</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A5</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>weapon_baseball_bat</t>
+          <t>mod_bullet_standard</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>废土棒球棍</t>
+          <t>标准子弹模块</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A14</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A17</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2996,22 +2996,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>mod_bullet_standard</t>
+          <t>item_ammo_pack</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>标准子弹模块</t>
+          <t>通用弹药</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>武器账本</t>
+          <t>物品道具账本</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A17</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -3043,27 +3043,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>melee_chaser</t>
+          <t>ranged_caster</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>item_ammo_pack</t>
+          <t>mod_bullet_piercing</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>通用弹药</t>
+          <t>穿甲弹模块</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>物品道具账本</t>
+          <t>武器账本</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A20</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>mod_bullet_piercing</t>
+          <t>mod_bullet_bounce</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>穿甲弹模块</t>
+          <t>回旋镖弹模块</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A20</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>mod_bullet_bounce</t>
+          <t>attach_scope</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>回旋镖弹模块</t>
+          <t>放大镜瞄具</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A19</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A27</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -3204,22 +3204,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>attach_scope</t>
+          <t>item_ammo_pack</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>放大镜瞄具</t>
+          <t>通用弹药</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>武器账本</t>
+          <t>物品道具账本</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A27</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -3251,27 +3251,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ranged_caster</t>
+          <t>exploder</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>item_ammo_pack</t>
+          <t>mod_bullet_explosive</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>通用弹药</t>
+          <t>爆炸弹模块</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>物品道具账本</t>
+          <t>武器账本</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
+          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A21</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -3308,22 +3308,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>mod_bullet_explosive</t>
+          <t>item_battery_s</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>爆炸弹模块</t>
+          <t>小型电池</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>武器账本</t>
+          <t>物品道具账本</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A21</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>item_battery_s</t>
+          <t>item_battery_l</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>小型电池</t>
+          <t>大型电池</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A21</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A22</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>item_battery_l</t>
+          <t>item_ammo_pack</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>大型电池</t>
+          <t>通用弹药</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A22</t>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3441,110 +3441,6 @@
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>src/rewards/RuntimeRewardCoordinator.gd#configure_level_drop_table / resolve_kill</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行13</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>expedition_01</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>exploder</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>weapon_launcher</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>反胃榴弹筒</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>武器账本</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_武器账本_v001.xlsx#背包物品调用索引!A12</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>data/level_plans/expedition_01/level_plan.json#monster_drop_table.rows[11]</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>src/rewards/MonsterDropTable.gd#compile</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>src/rewards/RuntimeRewardCoordinator.gd#configure_level_drop_table / resolve_kill</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>docs/v0.1/data/怪物掉落表_地图x怪物.csv#CSV行14</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>expedition_01</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>exploder</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>item_ammo_pack</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>通用弹药</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>物品道具账本</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>data/level_plans/expedition_01/level_plan.json#monster_drop_table.rows[12]</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>src/rewards/MonsterDropTable.gd#compile</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>src/rewards/RuntimeRewardCoordinator.gd#configure_level_drop_table / resolve_kill</t>
         </is>
@@ -3589,16 +3485,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId40"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId34"/>
   </tableParts>
 </worksheet>
 </file>

--- a/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx
@@ -553,9 +553,6 @@
           <t>物品道具账本</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
@@ -576,9 +573,6 @@
           <t>可掉落到地面、拾取进入背包的物品；内容ID唯一。子弹模块、配件及成品武器归武器账本；通用弹药归道具。</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -2763,7 +2757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2784,9 +2778,6 @@
           <t>怪物掉落归属导航</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
@@ -2797,12 +2788,9 @@
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>每行对应原CSV一行，仅指向登记所有者与运行投影。概率、数量与权重仍以原作者表及运行配置为准。</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
+          <t>每行对应一条掉落声明：远征01 指向原 CSV 一行，远征03 指向 level_plan 的 `monster_drop_table.rows[n]` / `clear_rewards.pickup.pool[n]` / `clear_rewards.ammo`。仅指向登记所有者与运行投影。概率、数量与权重仍以原作者表及运行配置为准。</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -3443,6 +3431,382 @@
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>src/rewards/RuntimeRewardCoordinator.gd#configure_level_drop_table / resolve_kill</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#monster_drop_table.rows[0]</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>expedition_03</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>egt_keybullet_kin</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>item_room_key</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>房间钥匙</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>物品道具账本</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#monster_drop_table.rows[0]</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>src/rewards/MonsterDropTable.gd#compile</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#monster_drop_table.rows[1]</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>expedition_03</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>egt_chance_kin</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>@pool:loot_floor_1_2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>浅层掉落池（1-2 层）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>武器账本 + 物品道具账本</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>src/rewards/RewardPoolRegistry.gd#POOLS.loot_floor_1_2</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#monster_drop_table.rows[1]</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>src/rewards/MonsterDropTable.gd#compile</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#clear_rewards.pickup.pool[0]</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>expedition_03</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>*（清房结算，非怪物）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>item_health_potion</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>治疗药水</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>物品道具账本</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A19</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#clear_rewards.pickup.pool[0]</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>src/map/FloorPlanGenerator.gd#_clear_reward_spec_for</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#clear_rewards.pickup.pool[1]</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>expedition_03</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>*（清房结算，非怪物）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>item_room_key</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>房间钥匙</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>物品道具账本</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#clear_rewards.pickup.pool[1]</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>src/map/FloorPlanGenerator.gd#_clear_reward_spec_for</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#clear_rewards.pickup.pool[2]</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>expedition_03</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>*（清房结算，非怪物）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>extraction_points</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>撤离点（战利品）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>货币通道（钱包，非物品）</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#monster_rules.currency</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#clear_rewards.pickup.pool[2]</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>src/map/FloorPlanGenerator.gd#_clear_reward_spec_for</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#clear_rewards.pickup.pool[3]</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>expedition_03</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>*（清房结算，非怪物）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>item_ammo_pack</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>通用弹药</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>物品道具账本</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#clear_rewards.pickup.pool[3]</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>src/map/FloorPlanGenerator.gd#_clear_reward_spec_for</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#clear_rewards.ammo</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>expedition_03</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>*（清房结算，非怪物）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>item_ammo_pack</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>通用弹药</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>物品道具账本</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_物品道具账本_v001.xlsx#物品道具!A20</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#clear_rewards.ammo</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>src/map/FloorPlanGenerator.gd#_clear_reward_spec_for</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#treasure_chests</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>expedition_03</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>*（宝箱房开箱，非怪物）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>@pool:loot_floor_1_2</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>浅层掉落池（1-2 层）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>武器账本 + 物品道具账本</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>src/rewards/RewardPoolRegistry.gd#POOLS.loot_floor_1_2</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>data/level_plans/expedition_03/level_plan.json#treasure_chests.reward_pool_id</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>src/world3d/Dungeon3D.gd#_on_chest_open_requested</t>
         </is>
       </c>
     </row>
@@ -3513,8 +3877,6 @@
           <t>非背包产出与待设计</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -3522,8 +3884,6 @@
           <t>货币与未注册设计条目显式排除，不冒充当前可入包物品。</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -3618,9 +3978,6 @@
           <t>物品功能调用链</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -3628,9 +3985,6 @@
           <t>账本仅导航；运行时不读取此XLSX，不另设物品、掉落或背包状态所有者。</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
